--- a/HU-Estructura67468.xlsx
+++ b/HU-Estructura67468.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://logiztikalliance-my.sharepoint.com/personal/systems4_logiztikalliance_com/Documents/Scripts Entidades/BDD ENTIDADES/Scripts Estructura/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{B1FF6F2E-3597-49D2-9634-D44C4B5488DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D827C691-B945-4F5D-A253-DEFA4DD55763}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{B1FF6F2E-3597-49D2-9634-D44C4B5488DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{642DA313-7F9E-46E8-84B8-79808B822D6A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="16536" windowHeight="8712" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia de implementación" sheetId="1" r:id="rId1"/>
@@ -489,9 +489,6 @@
     </r>
   </si>
   <si>
-    <t>https://lagcloud.visualstudio.com/AC%20Catalogos/_workitems/edit/55188</t>
-  </si>
-  <si>
     <t>Jesus Yandun</t>
   </si>
   <si>
@@ -643,6 +640,9 @@
   </si>
   <si>
     <t>Luis Campos</t>
+  </si>
+  <si>
+    <t>https://lagcloud.visualstudio.com/AC%20Catalogos/_workitems/edit/67468</t>
   </si>
 </sst>
 </file>
@@ -1939,60 +1939,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2092,6 +2038,57 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2164,6 +2161,9 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2190,7 +2190,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -11684,7 +11684,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -11984,7 +11984,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A2:P78"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
@@ -12003,44 +12003,44 @@
   <sheetData>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:16" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="114" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="O3" s="78" t="s">
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="O3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="P3" s="79"/>
+      <c r="P3" s="111"/>
     </row>
     <row r="4" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="87" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
+      <c r="B4" s="119" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
       <c r="O4" s="20" t="s">
         <v>2</v>
       </c>
@@ -12050,20 +12050,20 @@
       <c r="A5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="90" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91"/>
-      <c r="M5" s="91"/>
+      <c r="B5" s="122" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
       <c r="O5" s="14" t="s">
         <v>4</v>
       </c>
@@ -12073,20 +12073,20 @@
       <c r="A6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="80">
+      <c r="B6" s="112">
         <v>46177</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="113"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
     </row>
@@ -12094,18 +12094,18 @@
       <c r="A7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
+      <c r="B7" s="124"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="126"/>
+      <c r="M7" s="126"/>
     </row>
     <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
@@ -12123,21 +12123,21 @@
       <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:16" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="85"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="86"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
     </row>
     <row r="10" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -12234,67 +12234,67 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="109"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="92"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
     </row>
     <row r="15" spans="1:16" s="75" customFormat="1" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="109"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="110"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
     </row>
     <row r="16" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
-      <c r="B16" s="105"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="105"/>
-      <c r="L16" s="105"/>
-      <c r="M16" s="105"/>
+      <c r="A16" s="86"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
     </row>
     <row r="17" spans="1:13" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="106" t="s">
+      <c r="A17" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="107"/>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="107"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="108"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="108"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="90"/>
     </row>
     <row r="18" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -12304,18 +12304,18 @@
       <c r="C18" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="111" t="s">
+      <c r="D18" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="114"/>
-      <c r="L18" s="114"/>
-      <c r="M18" s="114"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
     </row>
     <row r="19" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -12325,16 +12325,16 @@
         <v>102</v>
       </c>
       <c r="C19" s="43"/>
-      <c r="D19" s="112"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="116"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="97"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="98"/>
     </row>
     <row r="20" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -12344,16 +12344,16 @@
         <v>102</v>
       </c>
       <c r="C20" s="43"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="116"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="98"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="98"/>
     </row>
     <row r="21" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -12363,20 +12363,20 @@
         <v>102</v>
       </c>
       <c r="C21" s="43"/>
-      <c r="D21" s="123" t="s">
+      <c r="D21" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="125" t="s">
+      <c r="E21" s="107" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96"/>
-      <c r="M21" s="96"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
     </row>
     <row r="22" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -12386,48 +12386,48 @@
       <c r="C22" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="D22" s="124"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="127"/>
-      <c r="K22" s="127"/>
-      <c r="L22" s="127"/>
-      <c r="M22" s="127"/>
+      <c r="D22" s="106"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
     </row>
     <row r="23" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="118"/>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="120"/>
-      <c r="L23" s="120"/>
-      <c r="M23" s="120"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="102"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="102"/>
     </row>
     <row r="24" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="121" t="s">
+      <c r="A24" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="122"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="122"/>
-      <c r="L24" s="122"/>
-      <c r="M24" s="122"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="104"/>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
@@ -12439,1010 +12439,1017 @@
       <c r="C25" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="117" t="s">
+      <c r="D25" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="117"/>
-      <c r="K25" s="117"/>
-      <c r="L25" s="117"/>
-      <c r="M25" s="117"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="99"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="99"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="99"/>
     </row>
     <row r="26" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="32">
         <v>1</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C26" s="33"/>
-      <c r="D26" s="95" t="s">
-        <v>108</v>
-      </c>
-      <c r="E26" s="96"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="96"/>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="96"/>
-      <c r="L26" s="96"/>
-      <c r="M26" s="97"/>
+      <c r="D26" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="78"/>
+      <c r="M26" s="79"/>
     </row>
     <row r="27" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="32">
         <v>2</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C27" s="33"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="99"/>
-      <c r="L27" s="99"/>
-      <c r="M27" s="100"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="82"/>
     </row>
     <row r="28" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="32">
         <v>3</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" s="33"/>
-      <c r="D28" s="98"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="99"/>
-      <c r="H28" s="99"/>
-      <c r="I28" s="99"/>
-      <c r="J28" s="99"/>
-      <c r="K28" s="99"/>
-      <c r="L28" s="99"/>
-      <c r="M28" s="100"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
+      <c r="M28" s="82"/>
     </row>
     <row r="29" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="32">
         <v>4</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C29" s="33"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="99"/>
-      <c r="G29" s="99"/>
-      <c r="H29" s="99"/>
-      <c r="I29" s="99"/>
-      <c r="J29" s="99"/>
-      <c r="K29" s="99"/>
-      <c r="L29" s="99"/>
-      <c r="M29" s="100"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="82"/>
     </row>
     <row r="30" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="32">
         <v>5</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C30" s="33"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="99"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="99"/>
-      <c r="I30" s="99"/>
-      <c r="J30" s="99"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="100"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="81"/>
+      <c r="M30" s="82"/>
     </row>
     <row r="31" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="32">
         <v>6</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C31" s="33"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="99"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="99"/>
-      <c r="M31" s="100"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
+      <c r="M31" s="82"/>
     </row>
     <row r="32" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="32">
         <v>7</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C32" s="33"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="99"/>
-      <c r="G32" s="99"/>
-      <c r="H32" s="99"/>
-      <c r="I32" s="99"/>
-      <c r="J32" s="99"/>
-      <c r="K32" s="99"/>
-      <c r="L32" s="99"/>
-      <c r="M32" s="100"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
+      <c r="M32" s="82"/>
     </row>
     <row r="33" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="32">
         <v>8</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33" s="33"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="99"/>
-      <c r="L33" s="99"/>
-      <c r="M33" s="100"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="82"/>
     </row>
     <row r="34" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="32">
         <v>9</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C34" s="33"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="99"/>
-      <c r="F34" s="99"/>
-      <c r="G34" s="99"/>
-      <c r="H34" s="99"/>
-      <c r="I34" s="99"/>
-      <c r="J34" s="99"/>
-      <c r="K34" s="99"/>
-      <c r="L34" s="99"/>
-      <c r="M34" s="100"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
+      <c r="M34" s="82"/>
     </row>
     <row r="35" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="32">
         <v>10</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C35" s="33"/>
-      <c r="D35" s="98"/>
-      <c r="E35" s="99"/>
-      <c r="F35" s="99"/>
-      <c r="G35" s="99"/>
-      <c r="H35" s="99"/>
-      <c r="I35" s="99"/>
-      <c r="J35" s="99"/>
-      <c r="K35" s="99"/>
-      <c r="L35" s="99"/>
-      <c r="M35" s="100"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="81"/>
+      <c r="L35" s="81"/>
+      <c r="M35" s="82"/>
     </row>
     <row r="36" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="32">
         <v>11</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C36" s="33"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="99"/>
-      <c r="F36" s="99"/>
-      <c r="G36" s="99"/>
-      <c r="H36" s="99"/>
-      <c r="I36" s="99"/>
-      <c r="J36" s="99"/>
-      <c r="K36" s="99"/>
-      <c r="L36" s="99"/>
-      <c r="M36" s="100"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="81"/>
+      <c r="L36" s="81"/>
+      <c r="M36" s="82"/>
     </row>
     <row r="37" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="32">
         <v>12</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C37" s="33"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="99"/>
-      <c r="K37" s="99"/>
-      <c r="L37" s="99"/>
-      <c r="M37" s="100"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
+      <c r="M37" s="82"/>
     </row>
     <row r="38" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="32">
         <v>13</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C38" s="33"/>
-      <c r="D38" s="98"/>
-      <c r="E38" s="99"/>
-      <c r="F38" s="99"/>
-      <c r="G38" s="99"/>
-      <c r="H38" s="99"/>
-      <c r="I38" s="99"/>
-      <c r="J38" s="99"/>
-      <c r="K38" s="99"/>
-      <c r="L38" s="99"/>
-      <c r="M38" s="100"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
+      <c r="M38" s="82"/>
     </row>
     <row r="39" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="32">
         <v>14</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C39" s="33"/>
-      <c r="D39" s="98"/>
-      <c r="E39" s="99"/>
-      <c r="F39" s="99"/>
-      <c r="G39" s="99"/>
-      <c r="H39" s="99"/>
-      <c r="I39" s="99"/>
-      <c r="J39" s="99"/>
-      <c r="K39" s="99"/>
-      <c r="L39" s="99"/>
-      <c r="M39" s="100"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="81"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="81"/>
+      <c r="M39" s="82"/>
     </row>
     <row r="40" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="32">
         <v>15</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C40" s="33"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="99"/>
-      <c r="F40" s="99"/>
-      <c r="G40" s="99"/>
-      <c r="H40" s="99"/>
-      <c r="I40" s="99"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="99"/>
-      <c r="L40" s="99"/>
-      <c r="M40" s="100"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="81"/>
+      <c r="M40" s="82"/>
     </row>
     <row r="41" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="32">
         <v>16</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C41" s="33"/>
-      <c r="D41" s="98"/>
-      <c r="E41" s="99"/>
-      <c r="F41" s="99"/>
-      <c r="G41" s="99"/>
-      <c r="H41" s="99"/>
-      <c r="I41" s="99"/>
-      <c r="J41" s="99"/>
-      <c r="K41" s="99"/>
-      <c r="L41" s="99"/>
-      <c r="M41" s="100"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="81"/>
+      <c r="J41" s="81"/>
+      <c r="K41" s="81"/>
+      <c r="L41" s="81"/>
+      <c r="M41" s="82"/>
     </row>
     <row r="42" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="32">
         <v>17</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C42" s="33"/>
-      <c r="D42" s="98"/>
-      <c r="E42" s="99"/>
-      <c r="F42" s="99"/>
-      <c r="G42" s="99"/>
-      <c r="H42" s="99"/>
-      <c r="I42" s="99"/>
-      <c r="J42" s="99"/>
-      <c r="K42" s="99"/>
-      <c r="L42" s="99"/>
-      <c r="M42" s="100"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
+      <c r="M42" s="82"/>
     </row>
     <row r="43" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32">
         <v>18</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C43" s="33"/>
-      <c r="D43" s="98"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="100"/>
+      <c r="D43" s="80"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="81"/>
+      <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="32">
         <v>19</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C44" s="33"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="99"/>
-      <c r="F44" s="99"/>
-      <c r="G44" s="99"/>
-      <c r="H44" s="99"/>
-      <c r="I44" s="99"/>
-      <c r="J44" s="99"/>
-      <c r="K44" s="99"/>
-      <c r="L44" s="99"/>
-      <c r="M44" s="100"/>
+      <c r="D44" s="80"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
+      <c r="M44" s="82"/>
     </row>
     <row r="45" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="32">
         <v>20</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C45" s="33"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="99"/>
-      <c r="F45" s="99"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="99"/>
-      <c r="I45" s="99"/>
-      <c r="J45" s="99"/>
-      <c r="K45" s="99"/>
-      <c r="L45" s="99"/>
-      <c r="M45" s="100"/>
+      <c r="D45" s="80"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
+      <c r="I45" s="81"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="81"/>
+      <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="32">
         <v>21</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C46" s="33"/>
-      <c r="D46" s="98"/>
-      <c r="E46" s="99"/>
-      <c r="F46" s="99"/>
-      <c r="G46" s="99"/>
-      <c r="H46" s="99"/>
-      <c r="I46" s="99"/>
-      <c r="J46" s="99"/>
-      <c r="K46" s="99"/>
-      <c r="L46" s="99"/>
-      <c r="M46" s="100"/>
+      <c r="D46" s="80"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="81"/>
+      <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="32">
         <v>22</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C47" s="33"/>
-      <c r="D47" s="98"/>
-      <c r="E47" s="99"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="99"/>
-      <c r="I47" s="99"/>
-      <c r="J47" s="99"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="100"/>
+      <c r="D47" s="80"/>
+      <c r="E47" s="81"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="81"/>
+      <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="32">
         <v>23</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C48" s="33"/>
-      <c r="D48" s="98"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="99"/>
-      <c r="I48" s="99"/>
-      <c r="J48" s="99"/>
-      <c r="K48" s="99"/>
-      <c r="L48" s="99"/>
-      <c r="M48" s="100"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
+      <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="32">
         <v>24</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="33"/>
-      <c r="D49" s="98"/>
-      <c r="E49" s="99"/>
-      <c r="F49" s="99"/>
-      <c r="G49" s="99"/>
-      <c r="H49" s="99"/>
-      <c r="I49" s="99"/>
-      <c r="J49" s="99"/>
-      <c r="K49" s="99"/>
-      <c r="L49" s="99"/>
-      <c r="M49" s="100"/>
+      <c r="D49" s="80"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
+      <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="32">
         <v>25</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="33"/>
-      <c r="D50" s="98"/>
-      <c r="E50" s="99"/>
-      <c r="F50" s="99"/>
-      <c r="G50" s="99"/>
-      <c r="H50" s="99"/>
-      <c r="I50" s="99"/>
-      <c r="J50" s="99"/>
-      <c r="K50" s="99"/>
-      <c r="L50" s="99"/>
-      <c r="M50" s="100"/>
+      <c r="D50" s="80"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
+      <c r="M50" s="82"/>
     </row>
     <row r="51" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="32">
         <v>26</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C51" s="33"/>
-      <c r="D51" s="98"/>
-      <c r="E51" s="99"/>
-      <c r="F51" s="99"/>
-      <c r="G51" s="99"/>
-      <c r="H51" s="99"/>
-      <c r="I51" s="99"/>
-      <c r="J51" s="99"/>
-      <c r="K51" s="99"/>
-      <c r="L51" s="99"/>
-      <c r="M51" s="100"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="81"/>
+      <c r="L51" s="81"/>
+      <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="32">
         <v>27</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C52" s="33"/>
-      <c r="D52" s="98"/>
-      <c r="E52" s="99"/>
-      <c r="F52" s="99"/>
-      <c r="G52" s="99"/>
-      <c r="H52" s="99"/>
-      <c r="I52" s="99"/>
-      <c r="J52" s="99"/>
-      <c r="K52" s="99"/>
-      <c r="L52" s="99"/>
-      <c r="M52" s="100"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="32">
         <v>28</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C53" s="33"/>
-      <c r="D53" s="98"/>
-      <c r="E53" s="99"/>
-      <c r="F53" s="99"/>
-      <c r="G53" s="99"/>
-      <c r="H53" s="99"/>
-      <c r="I53" s="99"/>
-      <c r="J53" s="99"/>
-      <c r="K53" s="99"/>
-      <c r="L53" s="99"/>
-      <c r="M53" s="100"/>
+      <c r="D53" s="80"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="82"/>
     </row>
     <row r="54" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="32">
         <v>29</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C54" s="33"/>
-      <c r="D54" s="98"/>
-      <c r="E54" s="99"/>
-      <c r="F54" s="99"/>
-      <c r="G54" s="99"/>
-      <c r="H54" s="99"/>
-      <c r="I54" s="99"/>
-      <c r="J54" s="99"/>
-      <c r="K54" s="99"/>
-      <c r="L54" s="99"/>
-      <c r="M54" s="100"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="82"/>
     </row>
     <row r="55" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="32">
         <v>30</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C55" s="33"/>
-      <c r="D55" s="98"/>
-      <c r="E55" s="99"/>
-      <c r="F55" s="99"/>
-      <c r="G55" s="99"/>
-      <c r="H55" s="99"/>
-      <c r="I55" s="99"/>
-      <c r="J55" s="99"/>
-      <c r="K55" s="99"/>
-      <c r="L55" s="99"/>
-      <c r="M55" s="100"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="82"/>
     </row>
     <row r="56" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="32">
         <v>31</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C56" s="33"/>
-      <c r="D56" s="98"/>
-      <c r="E56" s="99"/>
-      <c r="F56" s="99"/>
-      <c r="G56" s="99"/>
-      <c r="H56" s="99"/>
-      <c r="I56" s="99"/>
-      <c r="J56" s="99"/>
-      <c r="K56" s="99"/>
-      <c r="L56" s="99"/>
-      <c r="M56" s="100"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="82"/>
     </row>
     <row r="57" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="32">
         <v>32</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C57" s="33"/>
-      <c r="D57" s="98"/>
-      <c r="E57" s="99"/>
-      <c r="F57" s="99"/>
-      <c r="G57" s="99"/>
-      <c r="H57" s="99"/>
-      <c r="I57" s="99"/>
-      <c r="J57" s="99"/>
-      <c r="K57" s="99"/>
-      <c r="L57" s="99"/>
-      <c r="M57" s="100"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="82"/>
     </row>
     <row r="58" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="32">
         <v>33</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C58" s="33"/>
-      <c r="D58" s="98"/>
-      <c r="E58" s="99"/>
-      <c r="F58" s="99"/>
-      <c r="G58" s="99"/>
-      <c r="H58" s="99"/>
-      <c r="I58" s="99"/>
-      <c r="J58" s="99"/>
-      <c r="K58" s="99"/>
-      <c r="L58" s="99"/>
-      <c r="M58" s="100"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="81"/>
+      <c r="J58" s="81"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="82"/>
     </row>
     <row r="59" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="32">
         <v>34</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C59" s="33"/>
-      <c r="D59" s="98"/>
-      <c r="E59" s="99"/>
-      <c r="F59" s="99"/>
-      <c r="G59" s="99"/>
-      <c r="H59" s="99"/>
-      <c r="I59" s="99"/>
-      <c r="J59" s="99"/>
-      <c r="K59" s="99"/>
-      <c r="L59" s="99"/>
-      <c r="M59" s="100"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="81"/>
+      <c r="F59" s="81"/>
+      <c r="G59" s="81"/>
+      <c r="H59" s="81"/>
+      <c r="I59" s="81"/>
+      <c r="J59" s="81"/>
+      <c r="K59" s="81"/>
+      <c r="L59" s="81"/>
+      <c r="M59" s="82"/>
     </row>
     <row r="60" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="32">
         <v>35</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C60" s="33"/>
-      <c r="D60" s="98"/>
-      <c r="E60" s="99"/>
-      <c r="F60" s="99"/>
-      <c r="G60" s="99"/>
-      <c r="H60" s="99"/>
-      <c r="I60" s="99"/>
-      <c r="J60" s="99"/>
-      <c r="K60" s="99"/>
-      <c r="L60" s="99"/>
-      <c r="M60" s="100"/>
+      <c r="D60" s="80"/>
+      <c r="E60" s="81"/>
+      <c r="F60" s="81"/>
+      <c r="G60" s="81"/>
+      <c r="H60" s="81"/>
+      <c r="I60" s="81"/>
+      <c r="J60" s="81"/>
+      <c r="K60" s="81"/>
+      <c r="L60" s="81"/>
+      <c r="M60" s="82"/>
     </row>
     <row r="61" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="32">
         <v>36</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C61" s="33"/>
-      <c r="D61" s="98"/>
-      <c r="E61" s="99"/>
-      <c r="F61" s="99"/>
-      <c r="G61" s="99"/>
-      <c r="H61" s="99"/>
-      <c r="I61" s="99"/>
-      <c r="J61" s="99"/>
-      <c r="K61" s="99"/>
-      <c r="L61" s="99"/>
-      <c r="M61" s="100"/>
+      <c r="D61" s="80"/>
+      <c r="E61" s="81"/>
+      <c r="F61" s="81"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="81"/>
+      <c r="I61" s="81"/>
+      <c r="J61" s="81"/>
+      <c r="K61" s="81"/>
+      <c r="L61" s="81"/>
+      <c r="M61" s="82"/>
     </row>
     <row r="62" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="32">
         <v>37</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C62" s="33"/>
-      <c r="D62" s="98"/>
-      <c r="E62" s="99"/>
-      <c r="F62" s="99"/>
-      <c r="G62" s="99"/>
-      <c r="H62" s="99"/>
-      <c r="I62" s="99"/>
-      <c r="J62" s="99"/>
-      <c r="K62" s="99"/>
-      <c r="L62" s="99"/>
-      <c r="M62" s="100"/>
+      <c r="D62" s="80"/>
+      <c r="E62" s="81"/>
+      <c r="F62" s="81"/>
+      <c r="G62" s="81"/>
+      <c r="H62" s="81"/>
+      <c r="I62" s="81"/>
+      <c r="J62" s="81"/>
+      <c r="K62" s="81"/>
+      <c r="L62" s="81"/>
+      <c r="M62" s="82"/>
     </row>
     <row r="63" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="32">
         <v>38</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C63" s="33"/>
-      <c r="D63" s="98"/>
-      <c r="E63" s="99"/>
-      <c r="F63" s="99"/>
-      <c r="G63" s="99"/>
-      <c r="H63" s="99"/>
-      <c r="I63" s="99"/>
-      <c r="J63" s="99"/>
-      <c r="K63" s="99"/>
-      <c r="L63" s="99"/>
-      <c r="M63" s="100"/>
+      <c r="D63" s="80"/>
+      <c r="E63" s="81"/>
+      <c r="F63" s="81"/>
+      <c r="G63" s="81"/>
+      <c r="H63" s="81"/>
+      <c r="I63" s="81"/>
+      <c r="J63" s="81"/>
+      <c r="K63" s="81"/>
+      <c r="L63" s="81"/>
+      <c r="M63" s="82"/>
     </row>
     <row r="64" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="32">
         <v>39</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C64" s="33"/>
-      <c r="D64" s="98"/>
-      <c r="E64" s="99"/>
-      <c r="F64" s="99"/>
-      <c r="G64" s="99"/>
-      <c r="H64" s="99"/>
-      <c r="I64" s="99"/>
-      <c r="J64" s="99"/>
-      <c r="K64" s="99"/>
-      <c r="L64" s="99"/>
-      <c r="M64" s="100"/>
+      <c r="D64" s="80"/>
+      <c r="E64" s="81"/>
+      <c r="F64" s="81"/>
+      <c r="G64" s="81"/>
+      <c r="H64" s="81"/>
+      <c r="I64" s="81"/>
+      <c r="J64" s="81"/>
+      <c r="K64" s="81"/>
+      <c r="L64" s="81"/>
+      <c r="M64" s="82"/>
     </row>
     <row r="65" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="32">
         <v>40</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C65" s="33"/>
-      <c r="D65" s="98"/>
-      <c r="E65" s="99"/>
-      <c r="F65" s="99"/>
-      <c r="G65" s="99"/>
-      <c r="H65" s="99"/>
-      <c r="I65" s="99"/>
-      <c r="J65" s="99"/>
-      <c r="K65" s="99"/>
-      <c r="L65" s="99"/>
-      <c r="M65" s="100"/>
+      <c r="D65" s="80"/>
+      <c r="E65" s="81"/>
+      <c r="F65" s="81"/>
+      <c r="G65" s="81"/>
+      <c r="H65" s="81"/>
+      <c r="I65" s="81"/>
+      <c r="J65" s="81"/>
+      <c r="K65" s="81"/>
+      <c r="L65" s="81"/>
+      <c r="M65" s="82"/>
     </row>
     <row r="66" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="32">
         <v>41</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C66" s="33"/>
-      <c r="D66" s="98"/>
-      <c r="E66" s="99"/>
-      <c r="F66" s="99"/>
-      <c r="G66" s="99"/>
-      <c r="H66" s="99"/>
-      <c r="I66" s="99"/>
-      <c r="J66" s="99"/>
-      <c r="K66" s="99"/>
-      <c r="L66" s="99"/>
-      <c r="M66" s="100"/>
+      <c r="D66" s="80"/>
+      <c r="E66" s="81"/>
+      <c r="F66" s="81"/>
+      <c r="G66" s="81"/>
+      <c r="H66" s="81"/>
+      <c r="I66" s="81"/>
+      <c r="J66" s="81"/>
+      <c r="K66" s="81"/>
+      <c r="L66" s="81"/>
+      <c r="M66" s="82"/>
     </row>
     <row r="67" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="32">
         <v>42</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C67" s="33"/>
-      <c r="D67" s="98"/>
-      <c r="E67" s="99"/>
-      <c r="F67" s="99"/>
-      <c r="G67" s="99"/>
-      <c r="H67" s="99"/>
-      <c r="I67" s="99"/>
-      <c r="J67" s="99"/>
-      <c r="K67" s="99"/>
-      <c r="L67" s="99"/>
-      <c r="M67" s="100"/>
+      <c r="D67" s="80"/>
+      <c r="E67" s="81"/>
+      <c r="F67" s="81"/>
+      <c r="G67" s="81"/>
+      <c r="H67" s="81"/>
+      <c r="I67" s="81"/>
+      <c r="J67" s="81"/>
+      <c r="K67" s="81"/>
+      <c r="L67" s="81"/>
+      <c r="M67" s="82"/>
     </row>
     <row r="68" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="32">
         <v>43</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C68" s="33"/>
-      <c r="D68" s="98"/>
-      <c r="E68" s="99"/>
-      <c r="F68" s="99"/>
-      <c r="G68" s="99"/>
-      <c r="H68" s="99"/>
-      <c r="I68" s="99"/>
-      <c r="J68" s="99"/>
-      <c r="K68" s="99"/>
-      <c r="L68" s="99"/>
-      <c r="M68" s="100"/>
+      <c r="D68" s="80"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="81"/>
+      <c r="I68" s="81"/>
+      <c r="J68" s="81"/>
+      <c r="K68" s="81"/>
+      <c r="L68" s="81"/>
+      <c r="M68" s="82"/>
     </row>
     <row r="69" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="32">
         <v>44</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C69" s="33"/>
-      <c r="D69" s="98"/>
-      <c r="E69" s="99"/>
-      <c r="F69" s="99"/>
-      <c r="G69" s="99"/>
-      <c r="H69" s="99"/>
-      <c r="I69" s="99"/>
-      <c r="J69" s="99"/>
-      <c r="K69" s="99"/>
-      <c r="L69" s="99"/>
-      <c r="M69" s="100"/>
+      <c r="D69" s="80"/>
+      <c r="E69" s="81"/>
+      <c r="F69" s="81"/>
+      <c r="G69" s="81"/>
+      <c r="H69" s="81"/>
+      <c r="I69" s="81"/>
+      <c r="J69" s="81"/>
+      <c r="K69" s="81"/>
+      <c r="L69" s="81"/>
+      <c r="M69" s="82"/>
     </row>
     <row r="70" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="32">
         <v>45</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C70" s="33"/>
-      <c r="D70" s="98"/>
-      <c r="E70" s="99"/>
-      <c r="F70" s="99"/>
-      <c r="G70" s="99"/>
-      <c r="H70" s="99"/>
-      <c r="I70" s="99"/>
-      <c r="J70" s="99"/>
-      <c r="K70" s="99"/>
-      <c r="L70" s="99"/>
-      <c r="M70" s="100"/>
+      <c r="D70" s="80"/>
+      <c r="E70" s="81"/>
+      <c r="F70" s="81"/>
+      <c r="G70" s="81"/>
+      <c r="H70" s="81"/>
+      <c r="I70" s="81"/>
+      <c r="J70" s="81"/>
+      <c r="K70" s="81"/>
+      <c r="L70" s="81"/>
+      <c r="M70" s="82"/>
     </row>
     <row r="71" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="32">
         <v>46</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C71" s="33"/>
-      <c r="D71" s="98"/>
-      <c r="E71" s="99"/>
-      <c r="F71" s="99"/>
-      <c r="G71" s="99"/>
-      <c r="H71" s="99"/>
-      <c r="I71" s="99"/>
-      <c r="J71" s="99"/>
-      <c r="K71" s="99"/>
-      <c r="L71" s="99"/>
-      <c r="M71" s="100"/>
+      <c r="D71" s="80"/>
+      <c r="E71" s="81"/>
+      <c r="F71" s="81"/>
+      <c r="G71" s="81"/>
+      <c r="H71" s="81"/>
+      <c r="I71" s="81"/>
+      <c r="J71" s="81"/>
+      <c r="K71" s="81"/>
+      <c r="L71" s="81"/>
+      <c r="M71" s="82"/>
     </row>
     <row r="72" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="32">
         <v>47</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C72" s="33"/>
-      <c r="D72" s="98"/>
-      <c r="E72" s="99"/>
-      <c r="F72" s="99"/>
-      <c r="G72" s="99"/>
-      <c r="H72" s="99"/>
-      <c r="I72" s="99"/>
-      <c r="J72" s="99"/>
-      <c r="K72" s="99"/>
-      <c r="L72" s="99"/>
-      <c r="M72" s="100"/>
+      <c r="D72" s="80"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="81"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="81"/>
+      <c r="L72" s="81"/>
+      <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="32">
         <v>48</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C73" s="33"/>
-      <c r="D73" s="98"/>
-      <c r="E73" s="99"/>
-      <c r="F73" s="99"/>
-      <c r="G73" s="99"/>
-      <c r="H73" s="99"/>
-      <c r="I73" s="99"/>
-      <c r="J73" s="99"/>
-      <c r="K73" s="99"/>
-      <c r="L73" s="99"/>
-      <c r="M73" s="100"/>
+      <c r="D73" s="80"/>
+      <c r="E73" s="81"/>
+      <c r="F73" s="81"/>
+      <c r="G73" s="81"/>
+      <c r="H73" s="81"/>
+      <c r="I73" s="81"/>
+      <c r="J73" s="81"/>
+      <c r="K73" s="81"/>
+      <c r="L73" s="81"/>
+      <c r="M73" s="82"/>
     </row>
     <row r="74" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="32"/>
       <c r="B74" s="33"/>
       <c r="C74" s="33"/>
-      <c r="D74" s="98"/>
-      <c r="E74" s="99"/>
-      <c r="F74" s="99"/>
-      <c r="G74" s="99"/>
-      <c r="H74" s="99"/>
-      <c r="I74" s="99"/>
-      <c r="J74" s="99"/>
-      <c r="K74" s="99"/>
-      <c r="L74" s="99"/>
-      <c r="M74" s="100"/>
+      <c r="D74" s="80"/>
+      <c r="E74" s="81"/>
+      <c r="F74" s="81"/>
+      <c r="G74" s="81"/>
+      <c r="H74" s="81"/>
+      <c r="I74" s="81"/>
+      <c r="J74" s="81"/>
+      <c r="K74" s="81"/>
+      <c r="L74" s="81"/>
+      <c r="M74" s="82"/>
     </row>
     <row r="75" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="32"/>
       <c r="B75" s="33"/>
       <c r="C75" s="33"/>
-      <c r="D75" s="98"/>
-      <c r="E75" s="99"/>
-      <c r="F75" s="99"/>
-      <c r="G75" s="99"/>
-      <c r="H75" s="99"/>
-      <c r="I75" s="99"/>
-      <c r="J75" s="99"/>
-      <c r="K75" s="99"/>
-      <c r="L75" s="99"/>
-      <c r="M75" s="100"/>
+      <c r="D75" s="80"/>
+      <c r="E75" s="81"/>
+      <c r="F75" s="81"/>
+      <c r="G75" s="81"/>
+      <c r="H75" s="81"/>
+      <c r="I75" s="81"/>
+      <c r="J75" s="81"/>
+      <c r="K75" s="81"/>
+      <c r="L75" s="81"/>
+      <c r="M75" s="82"/>
     </row>
     <row r="76" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="32"/>
       <c r="B76" s="33"/>
       <c r="C76" s="33"/>
-      <c r="D76" s="98"/>
-      <c r="E76" s="99"/>
-      <c r="F76" s="99"/>
-      <c r="G76" s="99"/>
-      <c r="H76" s="99"/>
-      <c r="I76" s="99"/>
-      <c r="J76" s="99"/>
-      <c r="K76" s="99"/>
-      <c r="L76" s="99"/>
-      <c r="M76" s="100"/>
+      <c r="D76" s="80"/>
+      <c r="E76" s="81"/>
+      <c r="F76" s="81"/>
+      <c r="G76" s="81"/>
+      <c r="H76" s="81"/>
+      <c r="I76" s="81"/>
+      <c r="J76" s="81"/>
+      <c r="K76" s="81"/>
+      <c r="L76" s="81"/>
+      <c r="M76" s="82"/>
     </row>
     <row r="77" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="32"/>
       <c r="B77" s="33"/>
       <c r="C77" s="33"/>
-      <c r="D77" s="98"/>
-      <c r="E77" s="99"/>
-      <c r="F77" s="99"/>
-      <c r="G77" s="99"/>
-      <c r="H77" s="99"/>
-      <c r="I77" s="99"/>
-      <c r="J77" s="99"/>
-      <c r="K77" s="99"/>
-      <c r="L77" s="99"/>
-      <c r="M77" s="100"/>
+      <c r="D77" s="80"/>
+      <c r="E77" s="81"/>
+      <c r="F77" s="81"/>
+      <c r="G77" s="81"/>
+      <c r="H77" s="81"/>
+      <c r="I77" s="81"/>
+      <c r="J77" s="81"/>
+      <c r="K77" s="81"/>
+      <c r="L77" s="81"/>
+      <c r="M77" s="82"/>
     </row>
     <row r="78" spans="1:13" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="76"/>
       <c r="B78" s="33"/>
       <c r="C78" s="33"/>
-      <c r="D78" s="101"/>
-      <c r="E78" s="102"/>
-      <c r="F78" s="102"/>
-      <c r="G78" s="102"/>
-      <c r="H78" s="102"/>
-      <c r="I78" s="102"/>
-      <c r="J78" s="102"/>
-      <c r="K78" s="102"/>
-      <c r="L78" s="102"/>
-      <c r="M78" s="103"/>
+      <c r="D78" s="83"/>
+      <c r="E78" s="84"/>
+      <c r="F78" s="84"/>
+      <c r="G78" s="84"/>
+      <c r="H78" s="84"/>
+      <c r="I78" s="84"/>
+      <c r="J78" s="84"/>
+      <c r="K78" s="84"/>
+      <c r="L78" s="84"/>
+      <c r="M78" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B6:M6"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B7:M7"/>
     <mergeCell ref="D26:M78"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A17:M17"/>
@@ -13455,13 +13462,6 @@
     <mergeCell ref="A24:M24"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="E21:M22"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="B6:M6"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B7:M7"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
@@ -16742,7 +16742,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.33203125" bestFit="1" customWidth="1"/>
@@ -16753,50 +16753,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="139"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="138"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="142"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="141"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="143"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="145"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="144"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -16886,65 +16886,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="148"/>
-      <c r="C8" s="149"/>
-      <c r="D8" s="149"/>
-      <c r="E8" s="149"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="149"/>
-      <c r="H8" s="149"/>
-      <c r="I8" s="149"/>
-      <c r="J8" s="149"/>
-      <c r="K8" s="149"/>
-      <c r="L8" s="150"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="149"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="151"/>
-      <c r="C9" s="149"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="149"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="149"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="149"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="149"/>
-      <c r="L9" s="150"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="148"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="148"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="148"/>
+      <c r="I9" s="148"/>
+      <c r="J9" s="148"/>
+      <c r="K9" s="148"/>
+      <c r="L9" s="149"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="146" t="s">
+      <c r="A10" s="145" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="147"/>
-      <c r="C10" s="147"/>
-      <c r="D10" s="147"/>
-      <c r="E10" s="147"/>
-      <c r="F10" s="147"/>
-      <c r="G10" s="147"/>
-      <c r="H10" s="147"/>
-      <c r="I10" s="147"/>
-      <c r="J10" s="147"/>
-      <c r="K10" s="147"/>
-      <c r="L10" s="147"/>
+      <c r="B10" s="146"/>
+      <c r="C10" s="146"/>
+      <c r="D10" s="146"/>
+      <c r="E10" s="146"/>
+      <c r="F10" s="146"/>
+      <c r="G10" s="146"/>
+      <c r="H10" s="146"/>
+      <c r="I10" s="146"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="146"/>
+      <c r="L10" s="146"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="128" t="s">
+      <c r="A11" s="127" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="129"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-      <c r="J11" s="129"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="130"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="129"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
@@ -16956,101 +16956,101 @@
       <c r="C12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="117"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="117"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="99"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="48"/>
       <c r="B13" s="49"/>
       <c r="C13" s="49"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="133"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="132"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="48"/>
       <c r="B14" s="49"/>
       <c r="C14" s="49"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="135"/>
-      <c r="K14" s="135"/>
-      <c r="L14" s="136"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="134"/>
+      <c r="J14" s="134"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="135"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="48"/>
       <c r="B15" s="49"/>
       <c r="C15" s="49"/>
-      <c r="D15" s="134"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="136"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="135"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="48"/>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="136"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="134"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="135"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="135"/>
-      <c r="F17" s="135"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="135"/>
-      <c r="L17" s="136"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="134"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="135"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="48"/>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
-      <c r="L18" s="136"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -17127,7 +17127,7 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A4:M23"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" style="61" customWidth="1"/>
     <col min="2" max="2" width="128.109375" style="61" customWidth="1"/>
@@ -17139,10 +17139,10 @@
       <c r="B4" s="62"/>
     </row>
     <row r="6" spans="1:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="77"/>
+      <c r="B6" s="151"/>
     </row>
     <row r="8" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
@@ -17241,7 +17241,7 @@
         <v>44</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -17265,7 +17265,7 @@
         <v>47</v>
       </c>
       <c r="B14" s="74" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
@@ -17290,7 +17290,7 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B1:J23"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.6640625" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -17595,7 +17595,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
     <col min="2" max="2" width="208.44140625" bestFit="1" customWidth="1"/>
@@ -17740,7 +17740,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -17876,12 +17876,56 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18134,62 +18178,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18214,12 +18217,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>